--- a/self-rag/documents/LogAnalytics.xlsx
+++ b/self-rag/documents/LogAnalytics.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -448,13 +444,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Extra Details</t>
+          <t>Details</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>46133.375</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -478,13 +476,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-750C5348 | Method=AuthController.Logout</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>46133.37506944445</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -508,13 +508,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-1007ED73 | Method=CardController.BlockCard | ShellFleetHub.Exceptions.CardBlockedException: Fraud detection triggered
+   at ShellFleetHub.CardController.BlockCard(Card card)
+   at ShellFleetHub.Services.CardService.Block(Card card)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>46133.37513888889</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -538,13 +542,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-69649096 | Method=CardController.IssueCard | ShellFleetHub.Exceptions.CardBlockedException: Fraud detection triggered
+   at ShellFleetHub.CardController.BlockCard(Card card)
+   at ShellFleetHub.Services.CardService.Block(Card card)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>46133.37520833333</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -568,13 +576,15 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-5FB5377A | Method=CardController.BlockCard</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>46133.37527777778</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -598,13 +608,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-20582171 | Method=CardController.BlockCard | ShellFleetHub.Exceptions.TransactionDeclinedException: Balance below threshold
+   at ShellFleetHub.CardController.ProcessTransaction(Transaction txn)
+   at ShellFleetHub.Services.CardService.Execute(Transaction txn)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>46133.37534722222</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -628,13 +642,15 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-F8EBA01B | Method=AuthController.Login</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>46133.37541666667</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -658,13 +674,15 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-91EC14A2 | Method=CardController.ProcessTransaction</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>46133.37548611111</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -688,13 +706,15 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-33622A41 | Method=CardController.ProcessTransaction</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>46133.37555555555</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -718,13 +738,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-F05C0CDC | Method=AuthController.Login | ShellFleetHub.Exceptions.ValidationException: Invalid input
+   at ShellFleetHub.UserController.UpdateProfile(User user)
+   at ShellFleetHub.Services.UserService.Save(User user)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>46133.375625</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -748,13 +772,15 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-A6025E19 | Method=AuthController.Logout</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>46133.37569444445</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -778,13 +804,15 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-8D807E52 | Method=CardController.BlockCard</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>46133.37576388889</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -808,13 +836,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-0E4F9C9E | Method=AuthController.Logout | ShellFleetHub.Exceptions.ValidationException: Invalid input
+   at ShellFleetHub.UserController.UpdateProfile(User user)
+   at ShellFleetHub.Services.UserService.Save(User user)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>46133.37583333333</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -838,13 +870,15 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-34A3F3E6 | Method=AuthController.Logout</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>46133.37590277778</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -868,13 +902,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-09450A88 | Method=CardController.IssueCard | ShellFleetHub.Exceptions.TransactionDeclinedException: Balance below threshold
+   at ShellFleetHub.CardController.ProcessTransaction(Transaction txn)
+   at ShellFleetHub.Services.CardService.Execute(Transaction txn)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>46133.37597222222</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -898,13 +936,15 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-7A469218 | Method=AuthController.ResetPassword</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>46133.37604166667</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -928,13 +968,15 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-98E59BE9 | Method=CardController.BlockCard</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>46133.37611111111</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -958,13 +1000,15 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-FC85FF12 | Method=AuthController.ResetPassword</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>46133.37618055556</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -988,13 +1032,15 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-EA9AE8EA | Method=CardController.ProcessTransaction</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>46133.37625</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1018,13 +1064,15 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-D7CCB8EB | Method=CardController.ProcessTransaction</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>46133.37631944445</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1048,13 +1096,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-BEBB904A | Method=AuthController.ResetPassword | ShellFleetHub.AuthController.Logout(User user)
+   at ShellFleetHub.Services.AuthService.Terminate(User user)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>46133.37638888889</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1078,13 +1129,15 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-95F9019D | Method=UserController.UpdateProfile</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>46133.37645833333</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1108,13 +1161,15 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-28584BFA | Method=CardController.BlockCard</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>46133.37652777778</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1138,13 +1193,15 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-144967A2 | Method=CardController.ProcessTransaction</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>46133.37659722222</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1168,13 +1225,15 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-9CC7915F | Method=CardController.BlockCard</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>46133.37666666666</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1198,13 +1257,15 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-4499F473 | Method=AuthController.Logout</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>46133.37673611111</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1228,13 +1289,15 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-4E3DFD53 | Method=AuthController.Logout</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>46133.37680555556</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1258,13 +1321,15 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-8E544824 | Method=CardController.ProcessTransaction</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>46133.376875</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1288,13 +1353,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-25514D66 | Method=UserController.UpdateProfile | ShellFleetHub.AuthController.Logout(User user)
+   at ShellFleetHub.Services.AuthService.Terminate(User user)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>46133.37694444445</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1318,13 +1386,15 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-0DCEE345 | Method=AuthController.ResetPassword</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>46133.37701388889</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1348,13 +1418,15 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-3F83A7E0 | Method=AuthController.Logout</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>46133.37708333333</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1378,13 +1450,15 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-EE9338D1 | Method=AuthController.ResetPassword</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>46133.37715277778</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1408,13 +1482,15 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-DCAA3DD9 | Method=AuthController.Logout</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>46133.37722222223</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1438,13 +1514,15 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-A197F79B | Method=CardController.BlockCard</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>46133.37729166666</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1468,13 +1546,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-309A1887 | Method=CardController.ProcessTransaction | ShellFleetHub.Exceptions.CardBlockedException: Fraud detection triggered
+   at ShellFleetHub.CardController.BlockCard(Card card)
+   at ShellFleetHub.Services.CardService.Block(Card card)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>46133.37736111111</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1498,13 +1580,15 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-750606BD | Method=AuthController.Logout</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>46133.37743055556</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1528,13 +1612,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-3CD359D4 | Method=CardController.ProcessTransaction | ShellFleetHub.Exceptions.CardBlockedException: Fraud detection triggered
+   at ShellFleetHub.CardController.BlockCard(Card card)
+   at ShellFleetHub.Services.CardService.Block(Card card)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>46133.3775</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1558,13 +1646,15 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-7352B6BD | Method=CardController.IssueCard</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>46133.37756944444</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1588,13 +1678,15 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-248721FC | Method=CardController.ProcessTransaction</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>46133.37763888889</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1618,13 +1710,15 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-0DE482B9 | Method=AuthController.ResetPassword</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>46133.37770833333</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1648,13 +1742,15 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-8BE5F315 | Method=UserController.UpdateProfile</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>46133.37777777778</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1678,13 +1774,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-EB7A0BEC | Method=UserController.UpdateProfile | ShellFleetHub.Exceptions.ValidationException: Invalid input
+   at ShellFleetHub.UserController.UpdateProfile(User user)
+   at ShellFleetHub.Services.UserService.Save(User user)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>46133.37784722223</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1708,13 +1808,15 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-B5615A30 | Method=CardController.IssueCard</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>46133.37791666666</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1738,13 +1840,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-0B75DC3B | Method=CardController.ProcessTransaction | ShellFleetHub.Exceptions.CardDuplicateException: Card ID already exists
+   at ShellFleetHub.CardController.IssueCard(Card card)
+   at ShellFleetHub.Services.CardService.Create(Card card)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>46133.37798611111</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1768,13 +1874,15 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-021217E5 | Method=CardController.ProcessTransaction</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>46133.37805555556</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1798,13 +1906,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-EB7CC529 | Method=CardController.BlockCard | ShellFleetHub.Exceptions.CardBlockedException: Fraud detection triggered
+   at ShellFleetHub.CardController.BlockCard(Card card)
+   at ShellFleetHub.Services.CardService.Block(Card card)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>46133.378125</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1828,13 +1940,15 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-9A962C1F | Method=CardController.ProcessTransaction</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>46133.37819444444</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -1858,13 +1972,15 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-9BFD785F | Method=CardController.BlockCard</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>46133.37826388889</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1888,13 +2004,15 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-ED713B14 | Method=UserController.UpdateProfile</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>46133.37833333333</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -1918,13 +2036,15 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-5EBA9EDE | Method=UserController.UpdateProfile</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>46133.37840277778</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -1948,13 +2068,15 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-94732677 | Method=CardController.ProcessTransaction</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>46133.37847222222</v>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -1978,13 +2100,15 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-7CC754E2 | Method=CardController.IssueCard</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
-        <v>46133.37854166667</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2008,13 +2132,17 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-FF2B6DE2 | Method=CardController.ProcessTransaction | ShellFleetHub.Exceptions.CardBlockedException: Fraud detection triggered
+   at ShellFleetHub.CardController.BlockCard(Card card)
+   at ShellFleetHub.Services.CardService.Block(Card card)</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>46133.37861111111</v>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2038,13 +2166,15 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-66F78010 | Method=UserController.UpdateProfile</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>46133.37868055556</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2068,13 +2198,15 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-6CED0ED4 | Method=UserController.UpdateProfile</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>46133.37875</v>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2098,13 +2230,15 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-D2E1C258 | Method=CardController.BlockCard</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
-        <v>46133.37881944444</v>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2128,13 +2262,15 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-6F9F99E8 | Method=CardController.IssueCard</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
-        <v>46133.37888888889</v>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2158,13 +2294,16 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-B5E74899 | Method=AuthController.Logout | ShellFleetHub.AuthController.Logout(User user)
+   at ShellFleetHub.Services.AuthService.Terminate(User user)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
-        <v>46133.37895833333</v>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2188,13 +2327,17 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-2FA9F08F | Method=AuthController.Login | ShellFleetHub.Exceptions.ValidationException: Invalid input
+   at ShellFleetHub.UserController.UpdateProfile(User user)
+   at ShellFleetHub.Services.UserService.Save(User user)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
-        <v>46133.37902777778</v>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2218,13 +2361,17 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-88D0E2DA | Method=CardController.BlockCard | ShellFleetHub.Exceptions.CardBlockedException: Fraud detection triggered
+   at ShellFleetHub.CardController.BlockCard(Card card)
+   at ShellFleetHub.Services.CardService.Block(Card card)</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
-        <v>46133.37909722222</v>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2248,13 +2395,15 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-9AE23C99 | Method=CardController.ProcessTransaction</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
-        <v>46133.37916666667</v>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2278,13 +2427,15 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-30FF1E44 | Method=AuthController.ResetPassword</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
-        <v>46133.37923611111</v>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2308,13 +2459,15 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-2A337A51 | Method=UserController.UpdateProfile</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
-        <v>46133.37930555556</v>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2338,13 +2491,15 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-45D12093 | Method=AuthController.ResetPassword</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
-        <v>46133.379375</v>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2368,13 +2523,15 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-2A06FC5C | Method=AuthController.Login</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
-        <v>46133.37944444444</v>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -2398,13 +2555,15 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-DBE30FB7 | Method=CardController.ProcessTransaction</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
-        <v>46133.37951388889</v>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2428,13 +2587,15 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-9CC09038 | Method=AuthController.ResetPassword</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
-        <v>46133.37958333334</v>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -2458,13 +2619,15 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-6CE07BED | Method=AuthController.Logout</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
-        <v>46133.37965277778</v>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -2488,13 +2651,17 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-3D96B965 | Method=AuthController.ResetPassword | ShellFleetHub.Exceptions.ValidationException: Invalid input
+   at ShellFleetHub.UserController.UpdateProfile(User user)
+   at ShellFleetHub.Services.UserService.Save(User user)</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
-        <v>46133.37972222222</v>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -2518,13 +2685,15 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-0031FA9C | Method=CardController.ProcessTransaction</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
-        <v>46133.37979166667</v>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -2548,13 +2717,15 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-EBBB1AFA | Method=CardController.IssueCard</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
-        <v>46133.37986111111</v>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -2578,13 +2749,15 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-64289C54 | Method=AuthController.ResetPassword</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
-        <v>46133.37993055556</v>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -2608,13 +2781,17 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-FD8EBDC2 | Method=CardController.BlockCard | ShellFleetHub.Exceptions.CardBlockedException: Fraud detection triggered
+   at ShellFleetHub.CardController.BlockCard(Card card)
+   at ShellFleetHub.Services.CardService.Block(Card card)</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
-        <v>46133.38</v>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -2638,13 +2815,15 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-244C5583 | Method=CardController.BlockCard</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
-        <v>46133.38006944444</v>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -2668,13 +2847,16 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-9F7AB585 | Method=AuthController.ResetPassword | ShellFleetHub.AuthController.Login(User user)
+   at ShellFleetHub.Services.AuthService.Authenticate(User user)</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
-        <v>46133.38013888889</v>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -2698,13 +2880,15 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-AD12C2EA | Method=AuthController.Logout</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
-        <v>46133.38020833334</v>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -2728,13 +2912,16 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-DCAC9198 | Method=UserController.UpdateProfile | ShellFleetHub.AuthController.Login(User user)
+   at ShellFleetHub.Services.AuthService.Authenticate(User user)</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
-        <v>46133.38027777777</v>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -2758,13 +2945,15 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-280DA351 | Method=UserController.UpdateProfile</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
-        <v>46133.38034722222</v>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -2788,13 +2977,15 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-F5E2104E | Method=CardController.BlockCard</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
-        <v>46133.38041666667</v>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -2818,13 +3009,15 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-EDBAEEB6 | Method=CardController.IssueCard</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
-        <v>46133.38048611111</v>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -2848,13 +3041,16 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-CCD07164 | Method=AuthController.Logout | ShellFleetHub.AuthController.Login(User user)
+   at ShellFleetHub.Services.AuthService.Authenticate(User user)</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
-        <v>46133.38055555556</v>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -2878,13 +3074,15 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-5AAEB91F | Method=CardController.BlockCard</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
-        <v>46133.380625</v>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -2908,13 +3106,16 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-76EF435B | Method=UserController.UpdateProfile | ShellFleetHub.AuthController.Login(User user)
+   at ShellFleetHub.Services.AuthService.Authenticate(User user)</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
-        <v>46133.38069444444</v>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -2938,13 +3139,17 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-FEBC05E1 | Method=CardController.IssueCard | ShellFleetHub.Exceptions.CardBlockedException: Fraud detection triggered
+   at ShellFleetHub.CardController.BlockCard(Card card)
+   at ShellFleetHub.Services.CardService.Block(Card card)</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
-        <v>46133.38076388889</v>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -2968,13 +3173,15 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-EAE90C4E | Method=CardController.ProcessTransaction</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
-        <v>46133.38083333334</v>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -2998,13 +3205,17 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-CAE065E5 | Method=UserController.UpdateProfile | ShellFleetHub.Exceptions.ValidationException: Invalid input
+   at ShellFleetHub.UserController.UpdateProfile(User user)
+   at ShellFleetHub.Services.UserService.Save(User user)</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
-        <v>46133.38090277778</v>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -3028,13 +3239,15 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-7DAAAFE6 | Method=CardController.BlockCard</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
-        <v>46133.38097222222</v>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -3058,13 +3271,15 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-E8A8ADF6 | Method=UserController.UpdateProfile</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
-        <v>46133.38104166667</v>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -3088,13 +3303,17 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-C279B48A | Method=AuthController.Logout | ShellFleetHub.Exceptions.ValidationException: Invalid input
+   at ShellFleetHub.UserController.UpdateProfile(User user)
+   at ShellFleetHub.Services.UserService.Save(User user)</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
-        <v>46133.38111111111</v>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -3118,13 +3337,15 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-BB56D423 | Method=UserController.UpdateProfile</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
-        <v>46133.38118055555</v>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -3148,13 +3369,15 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-5B8EB129 | Method=CardController.ProcessTransaction</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
-        <v>46133.38125</v>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -3178,13 +3401,15 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-37A7C55B | Method=CardController.BlockCard</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
-        <v>46133.38131944444</v>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -3208,13 +3433,17 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-C82EAD5C | Method=UserController.UpdateProfile | ShellFleetHub.Exceptions.ValidationException: Invalid input
+   at ShellFleetHub.UserController.UpdateProfile(User user)
+   at ShellFleetHub.Services.UserService.Save(User user)</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
-        <v>46133.38138888889</v>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -3238,13 +3467,17 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-36BA37D6 | Method=CardController.BlockCard | ShellFleetHub.Exceptions.CardBlockedException: Fraud detection triggered
+   at ShellFleetHub.CardController.BlockCard(Card card)
+   at ShellFleetHub.Services.CardService.Block(Card card)</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
-        <v>46133.38145833334</v>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -3268,13 +3501,15 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-1DCD3EBB | Method=CardController.BlockCard</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
-        <v>46133.38152777778</v>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -3298,13 +3533,15 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-3D8DA5A3 | Method=CardController.IssueCard</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
-        <v>46133.38159722222</v>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -3328,13 +3565,16 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-2C7EB518 | Method=UserController.UpdateProfile | ShellFleetHub.AuthController.Login(User user)
+   at ShellFleetHub.Services.AuthService.Authenticate(User user)</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
-        <v>46133.38166666667</v>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -3358,13 +3598,15 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-04DA4726 | Method=AuthController.ResetPassword</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
-        <v>46133.38173611111</v>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -3388,13 +3630,17 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-BD8EEC33 | Method=CardController.ProcessTransaction | ShellFleetHub.Exceptions.CardBlockedException: Fraud detection triggered
+   at ShellFleetHub.CardController.BlockCard(Card card)
+   at ShellFleetHub.Services.CardService.Block(Card card)</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
-        <v>46133.38180555555</v>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -3418,13 +3664,17 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Issue</t>
+          <t>Issue | CorrelationId=REQ-26F38B18 | Method=CardController.ProcessTransaction | ShellFleetHub.Exceptions.CardDuplicateException: Card ID already exists
+   at ShellFleetHub.CardController.IssueCard(Card card)
+   at ShellFleetHub.Services.CardService.Create(Card card)</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
-        <v>46133.381875</v>
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:35</t>
+        </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -3448,7 +3698,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>OK | CorrelationId=REQ-A69E50C9 | Method=AuthController.Logout</t>
         </is>
       </c>
     </row>
